--- a/src/sto/stagiaires.xlsx
+++ b/src/sto/stagiaires.xlsx
@@ -398,38 +398,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BN23"/>
+  <dimension ref="A1:BN20"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="35.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="138.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="16.83203125" customWidth="1"/>
     <col min="12" max="12" width="19.83203125" customWidth="1"/>
-    <col min="13" max="13" width="25.83203125" customWidth="1"/>
+    <col min="13" max="13" width="24.83203125" customWidth="1"/>
     <col min="14" max="14" width="8.83203125" customWidth="1"/>
     <col min="15" max="15" width="20.83203125" customWidth="1"/>
     <col min="16" max="16" width="5.83203125" customWidth="1"/>
     <col min="17" max="17" width="16.83203125" customWidth="1"/>
     <col min="18" max="18" width="68.83203125" customWidth="1"/>
     <col min="19" max="19" width="18.83203125" customWidth="1"/>
-    <col min="20" max="20" width="21.83203125" customWidth="1"/>
+    <col min="20" max="20" width="19.83203125" customWidth="1"/>
     <col min="21" max="21" width="13.83203125" customWidth="1"/>
     <col min="22" max="22" width="28.83203125" customWidth="1"/>
-    <col min="23" max="23" width="60.83203125" customWidth="1"/>
+    <col min="23" max="23" width="30.83203125" customWidth="1"/>
     <col min="24" max="24" width="13.83203125" customWidth="1"/>
     <col min="25" max="25" width="28.83203125" customWidth="1"/>
     <col min="26" max="26" width="5.83203125" customWidth="1"/>
     <col min="27" max="27" width="10.83203125" customWidth="1"/>
     <col min="28" max="28" width="5.83203125" customWidth="1"/>
     <col min="29" max="29" width="20.83203125" customWidth="1"/>
-    <col min="30" max="30" width="26.83203125" customWidth="1"/>
+    <col min="30" max="30" width="22.83203125" customWidth="1"/>
     <col min="31" max="31" width="28.83203125" customWidth="1"/>
     <col min="32" max="32" width="5.83203125" customWidth="1"/>
     <col min="33" max="33" width="6.83203125" customWidth="1"/>
@@ -670,22 +670,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>135959</v>
+        <v>140513</v>
       </c>
       <c r="B2" t="str">
         <v>Femme</v>
       </c>
       <c r="C2" t="str">
-        <v>BRUYNEEL</v>
+        <v>ROBACHE</v>
       </c>
       <c r="D2" t="str">
-        <v>EMILY</v>
+        <v>TYPHAINE</v>
       </c>
       <c r="E2" t="str">
-        <v>e.bruyneel@e2c-grandlille.fr</v>
+        <v>t.robache@e2c-grandlille.fr</v>
       </c>
       <c r="F2" t="str">
-        <v>0625625034</v>
+        <v xml:space="preserve">07 44 94 95 08 </v>
       </c>
       <c r="G2" t="str">
         <v>Grand Lille</v>
@@ -694,31 +694,34 @@
         <v>Saint Omer</v>
       </c>
       <c r="I2" t="str">
-        <v>Auxiliaire de vie</v>
+        <v>Peintre en bâtiment, Employé / Employée de libre-service</v>
       </c>
       <c r="K2" t="str">
         <v>J'explore</v>
       </c>
       <c r="L2" t="str">
-        <v>référés Delphine</v>
+        <v>référés Bénédicte</v>
       </c>
       <c r="M2" t="str">
-        <v>2604/avril 2026 STO</v>
+        <v>2606/juin 2026 STO</v>
       </c>
       <c r="O2" t="str">
-        <v>HUDELLE Delphine</v>
+        <v>ROZIAU Bénédicte</v>
       </c>
       <c r="P2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R2" s="1">
-        <v>38829</v>
+        <v>40079</v>
       </c>
       <c r="S2" t="str">
-        <v>BRUYNEEL</v>
+        <v xml:space="preserve">ROBACHE </v>
+      </c>
+      <c r="T2" t="str">
+        <v>CALAIS</v>
       </c>
       <c r="U2" t="str">
         <v>FRANCAISE</v>
@@ -727,28 +730,25 @@
         <v>OUI</v>
       </c>
       <c r="W2" t="str">
-        <v>4 Rue du Bon Mariage</v>
+        <v>10 Rue de la Libération</v>
       </c>
       <c r="X2" t="str">
-        <v>62500</v>
+        <v>62219</v>
       </c>
       <c r="Y2" t="str">
-        <v>Saint-Omer</v>
+        <v>Longuenesse</v>
       </c>
       <c r="Z2" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>QN06237M</v>
+        <v>Non</v>
       </c>
       <c r="AB2" t="str">
         <v>Oui</v>
       </c>
       <c r="AC2" t="str">
-        <v>CEJ_FRANCE_TRAVAIL</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD2" t="str">
-        <v>4 validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE2" t="str">
         <v>Non</v>
@@ -760,7 +760,7 @@
         <v>SANS</v>
       </c>
       <c r="AH2" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AI2" t="str">
         <v>Non</v>
@@ -769,52 +769,52 @@
         <v>Non</v>
       </c>
       <c r="AK2" t="str">
-        <v>93h45m</v>
+        <v>90h</v>
       </c>
       <c r="AL2" t="str">
-        <v>116h25m</v>
+        <v>24h</v>
       </c>
       <c r="AM2" t="str">
-        <v>4h45m</v>
+        <v>48h45m</v>
       </c>
       <c r="AN2" s="1">
-        <v>46125.40116898148</v>
+        <v>46188.400775462964</v>
       </c>
       <c r="AP2" s="1">
-        <v>46400.413194444445</v>
+        <v>46461.46805555555</v>
       </c>
       <c r="AU2" s="1">
-        <v>46086.413194444445</v>
+        <v>45999.45625</v>
       </c>
       <c r="AV2" t="str">
-        <v>FRANCE TRAVAIL (LONGUENESSE)</v>
+        <v>MIPE</v>
       </c>
       <c r="AW2" t="str">
-        <v>MR LONGUEMART</v>
+        <v xml:space="preserve">STEPHANIE BERTIN </v>
       </c>
       <c r="AX2" s="1">
-        <v>46064.41527777778</v>
+        <v>45978.470138888886</v>
       </c>
       <c r="AY2" t="str">
-        <v>jerome.longuemart@francetravail.fr</v>
+        <v>bertin.s@lamipe-pso.fr</v>
       </c>
       <c r="AZ2" t="str">
-        <v>0617112529</v>
+        <v>06 74 93 14 32</v>
       </c>
       <c r="BA2" t="str">
         <v>NON</v>
       </c>
       <c r="BG2" t="str">
-        <v>14712</v>
+        <v>18742</v>
       </c>
       <c r="BH2" s="1">
-        <v>45917.083333333336</v>
+        <v>45931.083333333336</v>
       </c>
       <c r="BI2" t="str">
-        <v>1745976A</v>
+        <v>1748939W</v>
       </c>
       <c r="BJ2" t="str">
-        <v>9b0d3d26-cb57-4977-aa35-a42dca267564</v>
+        <v>7191a9c0-e194-49a5-adda-f0eb41b8d7ca</v>
       </c>
       <c r="BK2" t="str">
         <v>Accepted</v>
@@ -823,30 +823,30 @@
         <v/>
       </c>
       <c r="BM2" t="str">
-        <v>emilybruyneel62@gmail.com</v>
+        <v>typhaine62370@gmail.com</v>
       </c>
       <c r="BN2" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_bruyneel_e2c-grandlille_fr/IgDpj9Ek42TRSbUZ_wiQGr5zAVp3QJFc3mWulQxeChCAfLI?e=LzDqOV</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/t_robache_e2c-grandlille_fr/IgCpuIS-zTa7SaZSqUJWSkqZAagSpHefo6O5npCIhUIkIns?e=wwjZHX</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>135865</v>
+        <v>140392</v>
       </c>
       <c r="B3" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C3" t="str">
-        <v>HUGUET</v>
+        <v xml:space="preserve">VANROY </v>
       </c>
       <c r="D3" t="str">
-        <v>LEA</v>
+        <v xml:space="preserve">Clément </v>
       </c>
       <c r="E3" t="str">
-        <v>l.huguet@e2c-grandlille.fr</v>
+        <v>c.vanroy@e2c-grandlille.fr</v>
       </c>
       <c r="F3" t="str">
-        <v>0640136418</v>
+        <v>0624836700</v>
       </c>
       <c r="G3" t="str">
         <v>Grand Lille</v>
@@ -855,7 +855,7 @@
         <v>Saint Omer</v>
       </c>
       <c r="I3" t="str">
-        <v>Moniteur éducateur / Monitrice éducatrice, Agent territorial spécialisé / Agente territoriale spécialisée des écoles maternelles (ATSEM)</v>
+        <v>Employé / Employée de rayon, Secrétaire administratif / Secrétaire administrative</v>
       </c>
       <c r="K3" t="str">
         <v>J'ai des idées</v>
@@ -864,22 +864,22 @@
         <v>référés Bénédicte</v>
       </c>
       <c r="M3" t="str">
-        <v>2604/avril 2026 STO</v>
+        <v>2606/juin 2026 STO</v>
       </c>
       <c r="O3" t="str">
         <v>ROZIAU Bénédicte</v>
       </c>
       <c r="P3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R3" s="1">
-        <v>38423</v>
+        <v>36832</v>
       </c>
       <c r="S3" t="str">
-        <v>HUGUET</v>
+        <v>VANROY</v>
       </c>
       <c r="T3" t="str">
         <v>BLENDECQUES</v>
@@ -891,28 +891,28 @@
         <v>OUI</v>
       </c>
       <c r="W3" t="str">
-        <v>42 Rue Bernard Chochoy</v>
+        <v>15 Impasse des Clarisses</v>
       </c>
       <c r="X3" t="str">
-        <v>62380</v>
+        <v>62500</v>
       </c>
       <c r="Y3" t="str">
-        <v>Elnes</v>
+        <v>Saint-Omer</v>
       </c>
       <c r="Z3" t="str">
         <v>Non</v>
       </c>
       <c r="AB3" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AC3" t="str">
         <v>NON</v>
       </c>
       <c r="AD3" t="str">
-        <v>4 validé</v>
+        <v>4 non validé</v>
       </c>
       <c r="AE3" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AF3" t="str">
         <v>Non</v>
@@ -930,46 +930,46 @@
         <v>Non</v>
       </c>
       <c r="AK3" t="str">
-        <v>123h15m</v>
+        <v>132h15m</v>
       </c>
       <c r="AL3" t="str">
-        <v>58h30m</v>
+        <v>35h</v>
       </c>
       <c r="AM3" t="str">
         <v>6h30m</v>
       </c>
       <c r="AN3" s="1">
-        <v>46125.39949074074</v>
+        <v>46188.39915509259</v>
       </c>
       <c r="AP3" s="1">
-        <v>46400.604166666664</v>
+        <v>46461.45347222222</v>
       </c>
       <c r="AU3" s="1">
-        <v>46107.604166666664</v>
+        <v>46182.425</v>
       </c>
       <c r="AV3" t="str">
-        <v>RESEAUX SOCIAUX</v>
+        <v>DEA62</v>
       </c>
       <c r="AW3" t="str">
-        <v>SPONTANEE</v>
+        <v>CORALIE</v>
       </c>
       <c r="AX3" s="1">
-        <v>46104.60625</v>
+        <v>46175.42638888889</v>
       </c>
       <c r="BA3" t="str">
         <v>NON</v>
       </c>
       <c r="BG3" t="str">
-        <v>14608</v>
+        <v>18728</v>
       </c>
       <c r="BH3" s="1">
-        <v>45900.083333333336</v>
+        <v>45072.083333333336</v>
       </c>
       <c r="BI3" t="str">
-        <v>1679630K</v>
+        <v>1553844L</v>
       </c>
       <c r="BJ3" t="str">
-        <v>753ba25a-6a83-44d8-8790-79fa5cf1b8a6</v>
+        <v>ca29af85-dbd0-44e8-b546-aa66fc1dcad1</v>
       </c>
       <c r="BK3" t="str">
         <v>Accepted</v>
@@ -978,30 +978,30 @@
         <v/>
       </c>
       <c r="BM3" t="str">
-        <v>lea.huguet.62@icloud.com</v>
+        <v>vanroyclement62@gmail.com</v>
       </c>
       <c r="BN3" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_huguet_e2c-grandlille_fr/IgCEZrn-YvevS4AfnFXkd9KBARO_AjKO9EZpoW6IMjAlGxo?e=h0PYfT</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_vanroy_e2c-grandlille_fr/IgCE2N9njy8pSJykOWzZ_iByAWxKHHA49BOL0QdV7g4y0YM?e=3blTNn</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>135236</v>
+        <v>139806</v>
       </c>
       <c r="B4" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C4" t="str">
-        <v>SCHRIVE</v>
+        <v>CANET</v>
       </c>
       <c r="D4" t="str">
-        <v>Warren</v>
+        <v xml:space="preserve">CAMILLE </v>
       </c>
       <c r="E4" t="str">
-        <v>w.schrive@e2c-grandlille.fr</v>
+        <v>c.canet@e2c-grandlille.fr</v>
       </c>
       <c r="F4" t="str">
-        <v>0652662402</v>
+        <v>07 86 01 90 17</v>
       </c>
       <c r="G4" t="str">
         <v>Grand Lille</v>
@@ -1010,34 +1010,34 @@
         <v>Saint Omer</v>
       </c>
       <c r="I4" t="str">
-        <v>Agent / Agente d'entretien-propreté de locaux, Animateur / Animatrice d'accueil de loisirs (centre de loisirs)</v>
+        <v>Employé / Employée de rayon</v>
       </c>
       <c r="K4" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L4" t="str">
-        <v>référés Delphine</v>
+        <v>référés Cécile</v>
       </c>
       <c r="M4" t="str">
-        <v>2604/avril 2026 STO</v>
+        <v>2606/juin 2026 STO</v>
       </c>
       <c r="O4" t="str">
-        <v>HUDELLE Delphine</v>
+        <v>LECERF Cécile</v>
       </c>
       <c r="P4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R4" s="1">
-        <v>37226</v>
+        <v>38106</v>
       </c>
       <c r="S4" t="str">
-        <v>SCHRIVE</v>
+        <v xml:space="preserve">CANET </v>
       </c>
       <c r="T4" t="str">
-        <v>BLENDECQUES</v>
+        <v>CAYENNE</v>
       </c>
       <c r="U4" t="str">
         <v>FRANCAISE</v>
@@ -1046,28 +1046,28 @@
         <v>OUI</v>
       </c>
       <c r="W4" t="str">
-        <v>12 Rue Paul Dourlens</v>
+        <v>1 Rue Achille Castelnot</v>
       </c>
       <c r="X4" t="str">
-        <v>62219</v>
+        <v>62570</v>
       </c>
       <c r="Y4" t="str">
-        <v>Longuenesse</v>
+        <v>Wizernes</v>
       </c>
       <c r="Z4" t="str">
         <v>Non</v>
       </c>
       <c r="AB4" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AC4" t="str">
         <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD4" t="str">
-        <v>4 validé</v>
+        <v>4 non validé</v>
       </c>
       <c r="AE4" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AF4" t="str">
         <v>Non</v>
@@ -1085,52 +1085,52 @@
         <v>Non</v>
       </c>
       <c r="AK4" t="str">
-        <v>92h45m</v>
+        <v>138h45m</v>
       </c>
       <c r="AL4" t="str">
-        <v>94h</v>
+        <v>13h</v>
       </c>
       <c r="AM4" t="str">
-        <v>3h15m</v>
+        <v>0m</v>
       </c>
       <c r="AN4" s="1">
-        <v>46126.396886574075</v>
-      </c>
-      <c r="AO4" s="1">
-        <v>46171.66180555556</v>
+        <v>46188.39902777778</v>
       </c>
       <c r="AP4" s="1">
-        <v>46400.64861111111</v>
+        <v>46461.447916666664</v>
       </c>
       <c r="AU4" s="1">
-        <v>46119.64861111111</v>
+        <v>46171.458333333336</v>
       </c>
       <c r="AV4" t="str">
         <v>MIPE</v>
       </c>
       <c r="AW4" t="str">
-        <v>GREGORY LEROY</v>
+        <v xml:space="preserve">MARIE JADZAC </v>
       </c>
       <c r="AX4" s="1">
-        <v>46119.65069444444</v>
+        <v>46168.60208333333</v>
       </c>
       <c r="AY4" t="str">
-        <v>leroy.g@lamipe-pso.fr</v>
+        <v>jadczak .m@lamipe-pso.fr</v>
+      </c>
+      <c r="AZ4" t="str">
+        <v>06 78 00 31 04</v>
       </c>
       <c r="BA4" t="str">
-        <v>OUI</v>
+        <v>NON</v>
       </c>
       <c r="BG4" t="str">
-        <v>14713</v>
+        <v>18724</v>
       </c>
       <c r="BH4" s="1">
-        <v>45911.083333333336</v>
+        <v>46032.041666666664</v>
       </c>
       <c r="BI4" t="str">
-        <v>1744596A</v>
+        <v>1760602Y</v>
       </c>
       <c r="BJ4" t="str">
-        <v>96f63e9e-e04b-407b-89ae-96fb49028e0f</v>
+        <v>56e23466-38f1-46af-a4d7-4481678c2aac</v>
       </c>
       <c r="BK4" t="str">
         <v>Accepted</v>
@@ -1139,30 +1139,30 @@
         <v/>
       </c>
       <c r="BM4" t="str">
-        <v>wawan0402@gmail.com</v>
+        <v>camillecanet09@yahoo.com</v>
       </c>
       <c r="BN4" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/w_schrive_e2c-grandlille_fr/IgBHylO1ETR3Rqs0VFhHSNvDAdPIT0VhpLaljWGKj41h6PY?e=AHHiFX</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_canet_e2c-grandlille_fr/IgCVoq1G5ga-TZax22Ecq-8dAXOTrAH8sCfM06vHnlYXBGs?e=PB5SiA</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>120787</v>
+        <v>138732</v>
       </c>
       <c r="B5" t="str">
         <v>Homme</v>
       </c>
       <c r="C5" t="str">
-        <v>GOSLIN</v>
+        <v>HALLOT</v>
       </c>
       <c r="D5" t="str">
-        <v>Ewen</v>
+        <v>Elouan</v>
       </c>
       <c r="E5" t="str">
-        <v>e.goslin@e2c-grandlille.fr</v>
+        <v>e.hallot@e2c-grandlille.fr</v>
       </c>
       <c r="F5" t="str">
-        <v>0649842471</v>
+        <v>07 83 29 29 62</v>
       </c>
       <c r="G5" t="str">
         <v>Grand Lille</v>
@@ -1171,34 +1171,34 @@
         <v>Saint Omer</v>
       </c>
       <c r="I5" t="str">
-        <v>Employé / Employée de libre-service</v>
+        <v>Mécanicien / Mécanicienne automobile</v>
       </c>
       <c r="K5" t="str">
-        <v>J'ai des idées</v>
+        <v>J'explore</v>
       </c>
       <c r="L5" t="str">
-        <v>référés Bénédicte</v>
+        <v>référés Cécile</v>
       </c>
       <c r="M5" t="str">
-        <v>2604/avril 2026 STO</v>
+        <v>2606/juin 2026 STO</v>
       </c>
       <c r="O5" t="str">
-        <v>ROZIAU Bénédicte</v>
+        <v>LECERF Cécile</v>
       </c>
       <c r="P5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q5">
         <v>18</v>
       </c>
       <c r="R5" s="1">
-        <v>39201</v>
+        <v>39307</v>
       </c>
       <c r="S5" t="str">
-        <v>GOSLIN</v>
+        <v>HALLOT</v>
       </c>
       <c r="T5" t="str">
-        <v>CHARLEVILLE MEZIERE</v>
+        <v>BLENDECQUES</v>
       </c>
       <c r="U5" t="str">
         <v>FRANCAISE</v>
@@ -1207,13 +1207,13 @@
         <v>OUI</v>
       </c>
       <c r="W5" t="str">
-        <v>6 Rue Ernest Renan</v>
+        <v>76d Rue Louis le Sénéchal</v>
       </c>
       <c r="X5" t="str">
-        <v>62510</v>
+        <v>62570</v>
       </c>
       <c r="Y5" t="str">
-        <v>Arques</v>
+        <v>Hallines</v>
       </c>
       <c r="Z5" t="str">
         <v>Non</v>
@@ -1225,7 +1225,7 @@
         <v>NON</v>
       </c>
       <c r="AD5" t="str">
-        <v>4 non validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE5" t="str">
         <v>Non</v>
@@ -1246,46 +1246,46 @@
         <v>Non</v>
       </c>
       <c r="AK5" t="str">
-        <v>113h15m</v>
+        <v>135h30m</v>
       </c>
       <c r="AL5" t="str">
-        <v>84h</v>
+        <v>14h</v>
       </c>
       <c r="AM5" t="str">
-        <v>19h15m</v>
+        <v>3h15m</v>
       </c>
       <c r="AN5" s="1">
-        <v>46125.40152777778</v>
+        <v>46188.39945601852</v>
       </c>
       <c r="AP5" s="1">
-        <v>46400.67222222222</v>
+        <v>46461.447916666664</v>
       </c>
       <c r="AU5" s="1">
-        <v>46098.40347222222</v>
+        <v>46154.697222222225</v>
       </c>
       <c r="AV5" t="str">
-        <v>RESEAUX SOCIAUX</v>
+        <v>CIO SAINT-OMER</v>
       </c>
       <c r="AW5" t="str">
-        <v xml:space="preserve">FACEBOOK </v>
+        <v xml:space="preserve">CIO </v>
       </c>
       <c r="AX5" s="1">
-        <v>46097.40555555555</v>
+        <v>46147.69861111111</v>
       </c>
       <c r="BA5" t="str">
         <v>NON</v>
       </c>
       <c r="BG5" t="str">
-        <v>14620</v>
+        <v>18743</v>
       </c>
       <c r="BH5" s="1">
-        <v>45888.083333333336</v>
+        <v>46175.083333333336</v>
       </c>
       <c r="BI5" t="str">
-        <v>1739406J</v>
+        <v>1774270E</v>
       </c>
       <c r="BJ5" t="str">
-        <v>8f91ebe2-9f80-49a6-97d8-b5dc706dda6a</v>
+        <v>4a4ca35f-a7dd-4f19-b448-e165fc369d8e</v>
       </c>
       <c r="BK5" t="str">
         <v>Accepted</v>
@@ -1294,30 +1294,30 @@
         <v/>
       </c>
       <c r="BM5" t="str">
-        <v>ewengoslin30@gmail.com</v>
+        <v>elouan13@free.fr</v>
       </c>
       <c r="BN5" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_goslin_e2c-grandlille_fr/IgASCe-uToq2T6q3yDb8i9I0ASZbN7fy_se3ZvGkT3V-TSY?e=7MKgjx</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_hallot_e2c-grandlille_fr/IgB38HNkeXZMRZFQxtmdILHRAZ7Pe03lWW5KEozuXEMVFTU?e=mK67zb</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>118980</v>
+        <v>137553</v>
       </c>
       <c r="B6" t="str">
         <v>Femme</v>
       </c>
       <c r="C6" t="str">
-        <v>KIEKEN</v>
+        <v>FLAHAUT</v>
       </c>
       <c r="D6" t="str">
-        <v>Tiffanie</v>
+        <v>CELIA</v>
       </c>
       <c r="E6" t="str">
-        <v>t.kieken@e2c-grandlille.fr</v>
+        <v>c.flahaut@e2c-grandlille.fr</v>
       </c>
       <c r="F6" t="str">
-        <v>0661847065</v>
+        <v>0780202293</v>
       </c>
       <c r="G6" t="str">
         <v>Grand Lille</v>
@@ -1326,19 +1326,19 @@
         <v>Saint Omer</v>
       </c>
       <c r="I6" t="str">
-        <v>Auxiliaire de puériculture</v>
+        <v>Aide à domicile</v>
       </c>
       <c r="K6" t="str">
-        <v>J'explore</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L6" t="str">
-        <v>référés Cécile</v>
+        <v>référés Delphine</v>
       </c>
       <c r="M6" t="str">
-        <v>2604/avril 2026 STO</v>
+        <v>2606/juin 2026 STO</v>
       </c>
       <c r="O6" t="str">
-        <v>LECERF Cécile</v>
+        <v>HUDELLE Delphine</v>
       </c>
       <c r="P6">
         <v>18</v>
@@ -1347,13 +1347,13 @@
         <v>18</v>
       </c>
       <c r="R6" s="1">
-        <v>39351</v>
+        <v>39448</v>
       </c>
       <c r="S6" t="str">
-        <v>KIEKEN</v>
+        <v>FLAHAUT</v>
       </c>
       <c r="T6" t="str">
-        <v>CALAIS</v>
+        <v>RANG DU FLIERS</v>
       </c>
       <c r="U6" t="str">
         <v>FRANCAISE</v>
@@ -1362,13 +1362,13 @@
         <v>OUI</v>
       </c>
       <c r="W6" t="str">
-        <v>330 Route de Polincove</v>
+        <v>16 Rue Victor Hugo</v>
       </c>
       <c r="X6" t="str">
-        <v>62370</v>
+        <v>62380</v>
       </c>
       <c r="Y6" t="str">
-        <v>Audruicq</v>
+        <v>Lumbres</v>
       </c>
       <c r="Z6" t="str">
         <v>Non</v>
@@ -1380,7 +1380,7 @@
         <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD6" t="str">
-        <v>4 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE6" t="str">
         <v>Non</v>
@@ -1389,7 +1389,7 @@
         <v>Non</v>
       </c>
       <c r="AG6" t="str">
-        <v>AVEC</v>
+        <v>SANS</v>
       </c>
       <c r="AH6" t="str">
         <v>Non</v>
@@ -1401,49 +1401,49 @@
         <v>Non</v>
       </c>
       <c r="AK6" t="str">
-        <v>123h15m</v>
+        <v>108h</v>
       </c>
       <c r="AL6" t="str">
-        <v>84h</v>
+        <v>15h45m</v>
       </c>
       <c r="AM6" t="str">
-        <v>13h</v>
+        <v>30h45m</v>
       </c>
       <c r="AN6" s="1">
-        <v>46125.40179398148</v>
-      </c>
-      <c r="AO6" s="1">
-        <v>46175.635659722226</v>
+        <v>46188.40025462963</v>
       </c>
       <c r="AP6" s="1">
-        <v>46400.67569444444</v>
+        <v>46461.45486111111</v>
       </c>
       <c r="AU6" s="1">
-        <v>46100.70208333333</v>
+        <v>46126.49375</v>
       </c>
       <c r="AV6" t="str">
         <v>MIPE</v>
       </c>
       <c r="AW6" t="str">
-        <v>MALVINA</v>
+        <v>LEROY GREGORY</v>
       </c>
       <c r="AX6" s="1">
-        <v>46066.70416666667</v>
+        <v>46125.49652777778</v>
+      </c>
+      <c r="AY6" t="str">
+        <v>leroy.g@lamipe-pso.fr</v>
+      </c>
+      <c r="AZ6" t="str">
+        <v>06 74 93 14 56</v>
       </c>
       <c r="BA6" t="str">
         <v>NON</v>
       </c>
       <c r="BG6" t="str">
-        <v>14623</v>
-      </c>
-      <c r="BH6" s="1">
-        <v>45946.083333333336</v>
+        <v>18739</v>
       </c>
       <c r="BI6" t="str">
-        <v>1751234R</v>
+        <v>10508545952</v>
       </c>
       <c r="BJ6" t="str">
-        <v>82537299-ae29-4b1b-9d6c-e134800cc19f</v>
+        <v>32fc529a-bbac-4f4c-b17e-3cd766ee2ea8</v>
       </c>
       <c r="BK6" t="str">
         <v>Accepted</v>
@@ -1452,30 +1452,30 @@
         <v/>
       </c>
       <c r="BM6" t="str">
-        <v>tiffanie62370@gmail.com</v>
+        <v>flahautcelia2008@icloud.com</v>
       </c>
       <c r="BN6" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/t_kieken_e2c-grandlille_fr/IgBUyVXBqaogSriizSIu0qNwATLKblCUy33h2idTcYChmG8?e=dGuVIG</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_flahaut_e2c-grandlille_fr/IgArm6OOchRMSq_2H7wkOPD_AT5IdyNEkCaiQ7_dL4DVz2g?e=DDJk35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>118517</v>
+        <v>135959</v>
       </c>
       <c r="B7" t="str">
         <v>Femme</v>
       </c>
       <c r="C7" t="str">
-        <v>PECQUEUR--BOULY</v>
+        <v>BRUYNEEL</v>
       </c>
       <c r="D7" t="str">
-        <v>Typhaine</v>
+        <v>EMILY</v>
       </c>
       <c r="E7" t="str">
-        <v>t.pecqueurbouly@e2c-grandlille.fr</v>
+        <v>e.bruyneel@e2c-grandlille.fr</v>
       </c>
       <c r="F7" t="str">
-        <v>0784685826</v>
+        <v>0625625034</v>
       </c>
       <c r="G7" t="str">
         <v>Grand Lille</v>
@@ -1484,10 +1484,10 @@
         <v>Saint Omer</v>
       </c>
       <c r="I7" t="str">
-        <v>Jointeur / Jointeuse plaquiste, Peintre en bâtiment</v>
+        <v>Auxiliaire de vie</v>
       </c>
       <c r="K7" t="str">
-        <v>J'ai des idées</v>
+        <v>J'explore</v>
       </c>
       <c r="L7" t="str">
         <v>référés Delphine</v>
@@ -1499,16 +1499,16 @@
         <v>HUDELLE Delphine</v>
       </c>
       <c r="P7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R7" s="1">
-        <v>39338</v>
+        <v>38829</v>
       </c>
       <c r="S7" t="str">
-        <v>PECQUEUR--BOULY</v>
+        <v>BRUYNEEL</v>
       </c>
       <c r="T7" t="str">
         <v>BLENDECQUES</v>
@@ -1520,7 +1520,7 @@
         <v>OUI</v>
       </c>
       <c r="W7" t="str">
-        <v>127 Quai du Haut Pont</v>
+        <v>4 Rue du Bon Mariage</v>
       </c>
       <c r="X7" t="str">
         <v>62500</v>
@@ -1529,16 +1529,19 @@
         <v>Saint-Omer</v>
       </c>
       <c r="Z7" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>QN06237M</v>
       </c>
       <c r="AB7" t="str">
         <v>Oui</v>
       </c>
       <c r="AC7" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
+        <v>CEJ_FRANCE_TRAVAIL</v>
       </c>
       <c r="AD7" t="str">
-        <v>Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE7" t="str">
         <v>Non</v>
@@ -1547,7 +1550,7 @@
         <v>Non</v>
       </c>
       <c r="AG7" t="str">
-        <v>AVEC</v>
+        <v>SANS</v>
       </c>
       <c r="AH7" t="str">
         <v>Non</v>
@@ -1559,55 +1562,55 @@
         <v>Non</v>
       </c>
       <c r="AK7" t="str">
-        <v>116h45m</v>
+        <v>229h30m</v>
       </c>
       <c r="AL7" t="str">
-        <v>105h</v>
+        <v>217h55m</v>
       </c>
       <c r="AM7" t="str">
-        <v>13h</v>
+        <v>9h30m</v>
       </c>
       <c r="AN7" s="1">
-        <v>46125.40244212963</v>
+        <v>46125.40116898148</v>
       </c>
       <c r="AO7" s="1">
-        <v>46171.669444444444</v>
+        <v>46171.42013888889</v>
       </c>
       <c r="AP7" s="1">
-        <v>46400.674305555556</v>
+        <v>46400.413194444445</v>
       </c>
       <c r="AU7" s="1">
-        <v>46098.447916666664</v>
+        <v>46086.413194444445</v>
       </c>
       <c r="AV7" t="str">
-        <v>MIPE</v>
+        <v>FRANCE TRAVAIL (LONGUENESSE)</v>
       </c>
       <c r="AW7" t="str">
-        <v xml:space="preserve">MARYLISE PARENT </v>
+        <v>MR LONGUEMART</v>
       </c>
       <c r="AX7" s="1">
-        <v>46083.450694444444</v>
+        <v>46064.41527777778</v>
       </c>
       <c r="AY7" t="str">
-        <v>parent.m@lamipe-pso.fr</v>
+        <v>jerome.longuemart@francetravail.fr</v>
       </c>
       <c r="AZ7" t="str">
-        <v>06 78 00 38 88</v>
+        <v>0617112529</v>
       </c>
       <c r="BA7" t="str">
         <v>NON</v>
       </c>
       <c r="BG7" t="str">
-        <v>14589</v>
+        <v>14712</v>
       </c>
       <c r="BH7" s="1">
-        <v>45834.083333333336</v>
+        <v>45917.083333333336</v>
       </c>
       <c r="BI7" t="str">
-        <v>1732912A</v>
+        <v>1745976A</v>
       </c>
       <c r="BJ7" t="str">
-        <v>c8aa611f-fe4e-4c5c-9184-ee4695053378</v>
+        <v>9b0d3d26-cb57-4977-aa35-a42dca267564</v>
       </c>
       <c r="BK7" t="str">
         <v>Accepted</v>
@@ -1616,30 +1619,30 @@
         <v/>
       </c>
       <c r="BM7" t="str">
-        <v>typhainepecqueur13@gmail.com</v>
+        <v>emilybruyneel62@gmail.com</v>
       </c>
       <c r="BN7" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/t_pecqueurbouly_e2c-grandlille_fr/IgCe4oeU-aNlR4WsO3nl3H9DAdHBT6mla7jdCEtpJ_1Y-mI?e=Quz9l8</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_bruyneel_e2c-grandlille_fr/IgDpj9Ek42TRSbUZ_wiQGr5zAVp3QJFc3mWulQxeChCAfLI?e=LzDqOV</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>118484</v>
+        <v>135865</v>
       </c>
       <c r="B8" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C8" t="str">
-        <v>DEMARETZ</v>
+        <v>HUGUET</v>
       </c>
       <c r="D8" t="str">
-        <v>CLEMENT</v>
+        <v>LEA</v>
       </c>
       <c r="E8" t="str">
-        <v>c.demaretz@e2c-grandlille.fr</v>
+        <v>l.huguet@e2c-grandlille.fr</v>
       </c>
       <c r="F8" t="str">
-        <v>0745057553</v>
+        <v>0640136418</v>
       </c>
       <c r="G8" t="str">
         <v>Grand Lille</v>
@@ -1648,34 +1651,34 @@
         <v>Saint Omer</v>
       </c>
       <c r="I8" t="str">
-        <v>Employé polyvalent / Employée polyvalente de libre-service</v>
+        <v>Moniteur éducateur / Monitrice éducatrice, Agent territorial spécialisé / Agente territoriale spécialisée des écoles maternelles (ATSEM)</v>
       </c>
       <c r="K8" t="str">
         <v>J'ai des idées</v>
       </c>
       <c r="L8" t="str">
-        <v>référés Cécile</v>
+        <v>référés Bénédicte</v>
       </c>
       <c r="M8" t="str">
         <v>2604/avril 2026 STO</v>
       </c>
       <c r="O8" t="str">
-        <v>LECERF Cécile</v>
+        <v>ROZIAU Bénédicte</v>
       </c>
       <c r="P8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R8" s="1">
-        <v>37467</v>
+        <v>38423</v>
       </c>
       <c r="S8" t="str">
-        <v>DEMARETZ</v>
+        <v>HUGUET</v>
       </c>
       <c r="T8" t="str">
-        <v>ROUBAIX</v>
+        <v>BLENDECQUES</v>
       </c>
       <c r="U8" t="str">
         <v>FRANCAISE</v>
@@ -1684,13 +1687,13 @@
         <v>OUI</v>
       </c>
       <c r="W8" t="str">
-        <v>124 Rue de l’Europe</v>
+        <v>42 Rue Bernard Chochoy</v>
       </c>
       <c r="X8" t="str">
-        <v>62510</v>
+        <v>62380</v>
       </c>
       <c r="Y8" t="str">
-        <v>Arques</v>
+        <v>Elnes</v>
       </c>
       <c r="Z8" t="str">
         <v>Non</v>
@@ -1702,10 +1705,10 @@
         <v>NON</v>
       </c>
       <c r="AD8" t="str">
-        <v>4 non validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE8" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AF8" t="str">
         <v>Non</v>
@@ -1723,46 +1726,49 @@
         <v>Non</v>
       </c>
       <c r="AK8" t="str">
-        <v>94h</v>
+        <v>234h45m</v>
       </c>
       <c r="AL8" t="str">
-        <v>91h</v>
+        <v>115h15m</v>
       </c>
       <c r="AM8" t="str">
-        <v>42h15m</v>
+        <v>25h15m</v>
       </c>
       <c r="AN8" s="1">
-        <v>46125.40194444444</v>
+        <v>46125.39949074074</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>46171.5875</v>
       </c>
       <c r="AP8" s="1">
-        <v>46400.68125</v>
+        <v>46400.604166666664</v>
       </c>
       <c r="AU8" s="1">
-        <v>46098.425</v>
+        <v>46107.604166666664</v>
       </c>
       <c r="AV8" t="str">
         <v>RESEAUX SOCIAUX</v>
       </c>
       <c r="AW8" t="str">
-        <v>FACEBOOK</v>
+        <v>SPONTANEE</v>
       </c>
       <c r="AX8" s="1">
-        <v>46092.427777777775</v>
+        <v>46104.60625</v>
       </c>
       <c r="BA8" t="str">
         <v>NON</v>
       </c>
       <c r="BG8" t="str">
-        <v>14594</v>
+        <v>14608</v>
       </c>
       <c r="BH8" s="1">
-        <v>45737.041666666664</v>
+        <v>45900.083333333336</v>
       </c>
       <c r="BI8" t="str">
-        <v>1612230Z</v>
+        <v>1679630K</v>
       </c>
       <c r="BJ8" t="str">
-        <v>71a2269b-9a22-4374-b734-1a503fcccd8d</v>
+        <v>753ba25a-6a83-44d8-8790-79fa5cf1b8a6</v>
       </c>
       <c r="BK8" t="str">
         <v>Accepted</v>
@@ -1771,30 +1777,30 @@
         <v/>
       </c>
       <c r="BM8" t="str">
-        <v>clementdemaretz@gmail.com</v>
+        <v>lea.huguet.62@icloud.com</v>
       </c>
       <c r="BN8" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_demaretz_e2c-grandlille_fr/IgCD2k10xLkDTb_Txm_m5N4KAXWC2hKjRwDSyUQkYw9Gdf8?e=KnSU5i</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/l_huguet_e2c-grandlille_fr/IgCEZrn-YvevS4AfnFXkd9KBARO_AjKO9EZpoW6IMjAlGxo?e=h0PYfT</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>81744</v>
+        <v>135236</v>
       </c>
       <c r="B9" t="str">
         <v>Homme</v>
       </c>
       <c r="C9" t="str">
-        <v>EL HADDIOUI</v>
+        <v>SCHRIVE</v>
       </c>
       <c r="D9" t="str">
-        <v>Ayoub</v>
+        <v>Warren</v>
       </c>
       <c r="E9" t="str">
-        <v>a.elhaddioui@e2c-grandlille.fr</v>
+        <v>w.schrive@e2c-grandlille.fr</v>
       </c>
       <c r="F9" t="str">
-        <v>0784685823</v>
+        <v>0652662402</v>
       </c>
       <c r="G9" t="str">
         <v>Grand Lille</v>
@@ -1803,34 +1809,34 @@
         <v>Saint Omer</v>
       </c>
       <c r="I9" t="str">
-        <v>Employé / Employée de libre-service, Mécanicien / Mécanicienne automobile</v>
+        <v>Agent / Agente d'entretien-propreté de locaux, Animateur / Animatrice d'accueil de loisirs (centre de loisirs)</v>
       </c>
       <c r="K9" t="str">
-        <v>J'explore</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L9" t="str">
-        <v>référés Cécile</v>
+        <v>référés Delphine</v>
       </c>
       <c r="M9" t="str">
-        <v>2603/mars 2026 STO</v>
+        <v>2604/avril 2026 STO</v>
       </c>
       <c r="O9" t="str">
-        <v>LECERF Cécile</v>
+        <v>HUDELLE Delphine</v>
       </c>
       <c r="P9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R9" s="1">
-        <v>37430</v>
+        <v>37226</v>
       </c>
       <c r="S9" t="str">
-        <v>EL HADDIOUI</v>
+        <v>SCHRIVE</v>
       </c>
       <c r="T9" t="str">
-        <v>Mantes la Jolie</v>
+        <v>BLENDECQUES</v>
       </c>
       <c r="U9" t="str">
         <v>FRANCAISE</v>
@@ -1839,25 +1845,25 @@
         <v>OUI</v>
       </c>
       <c r="W9" t="str">
-        <v>50 Rue Jean Baptiste Colbert</v>
+        <v>12 Rue Paul Dourlens</v>
       </c>
       <c r="X9" t="str">
-        <v>62510</v>
+        <v>62219</v>
       </c>
       <c r="Y9" t="str">
-        <v>Arques</v>
+        <v>Longuenesse</v>
       </c>
       <c r="Z9" t="str">
         <v>Non</v>
       </c>
       <c r="AB9" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AC9" t="str">
         <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD9" t="str">
-        <v>Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE9" t="str">
         <v>Oui</v>
@@ -1878,22 +1884,25 @@
         <v>Non</v>
       </c>
       <c r="AK9" t="str">
-        <v>153h45m</v>
+        <v>131h30m</v>
       </c>
       <c r="AL9" t="str">
-        <v>144h45m</v>
+        <v>221h</v>
       </c>
       <c r="AM9" t="str">
-        <v>48h</v>
+        <v>16h15m</v>
       </c>
       <c r="AN9" s="1">
-        <v>46090.4440625</v>
+        <v>46126.396886574075</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>46171.66180555556</v>
       </c>
       <c r="AP9" s="1">
-        <v>46365.63402777778</v>
+        <v>46400.64861111111</v>
       </c>
       <c r="AU9" s="1">
-        <v>46070.583333333336</v>
+        <v>46119.64861111111</v>
       </c>
       <c r="AV9" t="str">
         <v>MIPE</v>
@@ -1902,25 +1911,25 @@
         <v>GREGORY LEROY</v>
       </c>
       <c r="AX9" s="1">
-        <v>46090.697222222225</v>
+        <v>46119.65069444444</v>
       </c>
       <c r="AY9" t="str">
         <v>leroy.g@lamipe-pso.fr</v>
       </c>
       <c r="BA9" t="str">
-        <v>NON</v>
+        <v>OUI</v>
       </c>
       <c r="BG9" t="str">
-        <v>11504</v>
+        <v>14713</v>
       </c>
       <c r="BH9" s="1">
-        <v>46041.041666666664</v>
+        <v>45911.083333333336</v>
       </c>
       <c r="BI9" t="str">
-        <v>1761526C</v>
+        <v>1744596A</v>
       </c>
       <c r="BJ9" t="str">
-        <v>1cc057dd-7342-4fdb-a93c-2bad249f2f02</v>
+        <v>96f63e9e-e04b-407b-89ae-96fb49028e0f</v>
       </c>
       <c r="BK9" t="str">
         <v>Accepted</v>
@@ -1929,30 +1938,30 @@
         <v/>
       </c>
       <c r="BM9" t="str">
-        <v>aelhaddpro@gmail.com</v>
+        <v>wawani0402@gmail.com</v>
       </c>
       <c r="BN9" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/a_elhaddioui_e2c-grandlille_fr/IgBDp2sCvJ7ARaN2mfmyb2H3AbZLastaLMyXxmcM_W5TESw?e=WVbyhK</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/w_schrive_e2c-grandlille_fr/IgBHylO1ETR3Rqs0VFhHSNvDAdPIT0VhpLaljWGKj41h6PY?e=AHHiFX</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>81726</v>
+        <v>131953</v>
       </c>
       <c r="B10" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C10" t="str">
-        <v>LEROY</v>
+        <v xml:space="preserve">LAMIRANT </v>
       </c>
       <c r="D10" t="str">
-        <v>Bryan</v>
+        <v>Clara</v>
       </c>
       <c r="E10" t="str">
-        <v>b.leroy@e2c-grandlille.fr</v>
+        <v>c.lamirant@e2c-grandlille.fr</v>
       </c>
       <c r="F10" t="str">
-        <v>0669220460</v>
+        <v>0662323892</v>
       </c>
       <c r="G10" t="str">
         <v>Grand Lille</v>
@@ -1961,34 +1970,34 @@
         <v>Saint Omer</v>
       </c>
       <c r="I10" t="str">
-        <v>Ouvrier polyvalent / Ouvrière polyvalente d'entretien des bâtiments</v>
+        <v>Agent / Agente d'entretien-propreté de locaux</v>
       </c>
       <c r="K10" t="str">
         <v>Je sais</v>
       </c>
       <c r="L10" t="str">
-        <v>référés Bénédicte</v>
+        <v>référés Delphine</v>
       </c>
       <c r="M10" t="str">
-        <v>2603/mars 2026 STO</v>
+        <v>2606/juin 2026 STO</v>
       </c>
       <c r="O10" t="str">
-        <v>ROZIAU Bénédicte</v>
+        <v>HUDELLE Delphine</v>
       </c>
       <c r="P10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R10" s="1">
-        <v>38618</v>
+        <v>39119</v>
       </c>
       <c r="S10" t="str">
-        <v>LEROY</v>
+        <v xml:space="preserve">LAMIRANT </v>
       </c>
       <c r="T10" t="str">
-        <v>Lille</v>
+        <v>CALAIS</v>
       </c>
       <c r="U10" t="str">
         <v>FRANCAISE</v>
@@ -1997,28 +2006,28 @@
         <v>OUI</v>
       </c>
       <c r="W10" t="str">
-        <v>428 Rue du Parfum des Sapins</v>
+        <v>95 Rue d'Artois</v>
       </c>
       <c r="X10" t="str">
-        <v>62570</v>
+        <v>62370</v>
       </c>
       <c r="Y10" t="str">
-        <v>Helfaut</v>
+        <v>Audruicq</v>
       </c>
       <c r="Z10" t="str">
         <v>Non</v>
       </c>
       <c r="AB10" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AC10" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD10" t="str">
-        <v>[OLD]Niveau Infra 3</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE10" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AF10" t="str">
         <v>Non</v>
@@ -2036,52 +2045,52 @@
         <v>Non</v>
       </c>
       <c r="AK10" t="str">
-        <v>123h15m</v>
+        <v>100h</v>
       </c>
       <c r="AL10" t="str">
-        <v>118h</v>
+        <v>35h</v>
       </c>
       <c r="AM10" t="str">
-        <v>48h45m</v>
+        <v>39h</v>
       </c>
       <c r="AN10" s="1">
-        <v>46090.445925925924</v>
-      </c>
-      <c r="AO10" s="1">
-        <v>46171.657638888886</v>
+        <v>46188.39983796296</v>
       </c>
       <c r="AP10" s="1">
-        <v>46365.447222222225</v>
+        <v>46461.64027777778</v>
       </c>
       <c r="AU10" s="1">
-        <v>46070.68958333333</v>
+        <v>46100.438888888886</v>
       </c>
       <c r="AV10" t="str">
         <v>MIPE</v>
       </c>
       <c r="AW10" t="str">
-        <v>GREGORY LEROY</v>
+        <v>MALVINA</v>
       </c>
       <c r="AX10" s="1">
-        <v>46063.69236111111</v>
+        <v>46069.44027777778</v>
       </c>
       <c r="AY10" t="str">
-        <v>leroy.g@lamipe-pso.fr</v>
+        <v>feramus.m@lamipe-pso.fr</v>
+      </c>
+      <c r="AZ10" t="str">
+        <v>0674931443</v>
       </c>
       <c r="BA10" t="str">
         <v>NON</v>
       </c>
       <c r="BG10" t="str">
-        <v>11914</v>
+        <v>18732</v>
       </c>
       <c r="BH10" s="1">
-        <v>45944.083333333336</v>
+        <v>45931.083333333336</v>
       </c>
       <c r="BI10" t="str">
-        <v>5952912G</v>
+        <v>10495666412</v>
       </c>
       <c r="BJ10" t="str">
-        <v>2f0f42dd-4cab-44e6-8162-ed08596a4a34</v>
+        <v>f893b64b-4ced-47fc-b28a-d8f90dd1c8d3</v>
       </c>
       <c r="BK10" t="str">
         <v>Accepted</v>
@@ -2090,30 +2099,30 @@
         <v/>
       </c>
       <c r="BM10" t="str">
-        <v>bryanleroy818@gmail.com</v>
+        <v>claralamirant9@gmail.com</v>
       </c>
       <c r="BN10" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/b_leroy_e2c-grandlille_fr/IgCZeMh98XI1To8-bMZAbt5bAQOhibxgjufYIEG7lhPUOwI?e=LOUtFq</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_lamirant_e2c-grandlille_fr/IgBoxdDxiEfmQIMxxb_e4Q8bARiYIObQg628eT-Ju10Fhnk?e=bPxmi4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>80870</v>
+        <v>118980</v>
       </c>
       <c r="B11" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C11" t="str">
-        <v>FOULON</v>
+        <v>KIEKEN</v>
       </c>
       <c r="D11" t="str">
-        <v>Mathéo</v>
+        <v>Tiffanie</v>
       </c>
       <c r="E11" t="str">
-        <v>m.foulon@e2c-grandlille.fr</v>
+        <v>t.kieken@e2c-grandlille.fr</v>
       </c>
       <c r="F11" t="str">
-        <v>0659048744</v>
+        <v>0661847065</v>
       </c>
       <c r="G11" t="str">
         <v>Grand Lille</v>
@@ -2122,34 +2131,34 @@
         <v>Saint Omer</v>
       </c>
       <c r="I11" t="str">
-        <v>Agent / Agente d'entretien des espaces verts</v>
+        <v>Auxiliaire de puériculture</v>
       </c>
       <c r="K11" t="str">
-        <v>Je sais</v>
+        <v>J'explore</v>
       </c>
       <c r="L11" t="str">
-        <v>référés Delphine</v>
+        <v>référés Cécile</v>
       </c>
       <c r="M11" t="str">
-        <v>2603/mars 2026 STO</v>
+        <v>2604/avril 2026 STO</v>
       </c>
       <c r="O11" t="str">
-        <v>HUDELLE Delphine</v>
+        <v>LECERF Cécile</v>
       </c>
       <c r="P11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R11" s="1">
-        <v>38169</v>
+        <v>39351</v>
       </c>
       <c r="S11" t="str">
-        <v xml:space="preserve">FOULON </v>
+        <v>KIEKEN</v>
       </c>
       <c r="T11" t="str">
-        <v>Chateau-gontier</v>
+        <v>CALAIS</v>
       </c>
       <c r="U11" t="str">
         <v>FRANCAISE</v>
@@ -2158,34 +2167,34 @@
         <v>OUI</v>
       </c>
       <c r="W11" t="str">
-        <v>3a Rue de l’Eglise Saint Maurice</v>
+        <v>330 Route de Polincove</v>
       </c>
       <c r="X11" t="str">
-        <v>62330</v>
+        <v>62370</v>
       </c>
       <c r="Y11" t="str">
-        <v>Isbergues</v>
+        <v>Audruicq</v>
       </c>
       <c r="Z11" t="str">
         <v>Non</v>
       </c>
       <c r="AB11" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AC11" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD11" t="str">
-        <v>[OLD]Niveau 3 non validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE11" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AF11" t="str">
         <v>Non</v>
       </c>
       <c r="AG11" t="str">
-        <v>SANS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH11" t="str">
         <v>Non</v>
@@ -2197,46 +2206,49 @@
         <v>Non</v>
       </c>
       <c r="AK11" t="str">
-        <v>103h</v>
+        <v>159h</v>
       </c>
       <c r="AL11" t="str">
-        <v>0m</v>
+        <v>231h</v>
       </c>
       <c r="AM11" t="str">
-        <v>26h</v>
+        <v>48h15m</v>
       </c>
       <c r="AN11" s="1">
-        <v>46090.45410879629</v>
+        <v>46125.40179398148</v>
       </c>
       <c r="AO11" s="1">
-        <v>46111.37430555555</v>
+        <v>46175.635659722226</v>
       </c>
       <c r="AP11" s="1">
-        <v>46365.475</v>
+        <v>46400.67569444444</v>
       </c>
       <c r="AU11" s="1">
-        <v>46063.683333333334</v>
+        <v>46100.70208333333</v>
       </c>
       <c r="AV11" t="str">
-        <v>En direct</v>
+        <v>MIPE</v>
+      </c>
+      <c r="AW11" t="str">
+        <v>MALVINA</v>
       </c>
       <c r="AX11" s="1">
-        <v>46063.45277777778</v>
+        <v>46066.70416666667</v>
       </c>
       <c r="BA11" t="str">
         <v>NON</v>
       </c>
       <c r="BG11" t="str">
-        <v>11041</v>
+        <v>14623</v>
       </c>
       <c r="BH11" s="1">
-        <v>45825.083333333336</v>
+        <v>45946.083333333336</v>
       </c>
       <c r="BI11" t="str">
-        <v>10517137061</v>
+        <v>1751234R</v>
       </c>
       <c r="BJ11" t="str">
-        <v>224e0948-8083-45c2-bc89-9355da9220b0</v>
+        <v>82537299-ae29-4b1b-9d6c-e134800cc19f</v>
       </c>
       <c r="BK11" t="str">
         <v>Accepted</v>
@@ -2245,30 +2257,30 @@
         <v/>
       </c>
       <c r="BM11" t="str">
-        <v>matheof270@gmail.com</v>
+        <v>tiffanie62370@gmail.com</v>
       </c>
       <c r="BN11" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_foulon_e2c-grandlille_fr/IgARpSxSFX9ER4ZxL6_N35nEAZhdE_cnHeahEiPoqHPCxKI?e=9h1gRE</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/t_kieken_e2c-grandlille_fr/IgBUyVXBqaogSriizSIu0qNwATLKblCUy33h2idTcYChmG8?e=dGuVIG</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>80337</v>
+        <v>118517</v>
       </c>
       <c r="B12" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C12" t="str">
-        <v>NOEL</v>
+        <v>PECQUEUR--BOULY</v>
       </c>
       <c r="D12" t="str">
-        <v>Romain</v>
+        <v>Typhaine</v>
       </c>
       <c r="E12" t="str">
-        <v>r.noel@e2c-grandlille.fr</v>
+        <v>t.pecqueurbouly@e2c-grandlille.fr</v>
       </c>
       <c r="F12" t="str">
-        <v>0615066410</v>
+        <v>0784685826</v>
       </c>
       <c r="G12" t="str">
         <v>Grand Lille</v>
@@ -2277,31 +2289,31 @@
         <v>Saint Omer</v>
       </c>
       <c r="I12" t="str">
-        <v>Employé / Employée de libre-service</v>
+        <v>Jointeur / Jointeuse plaquiste, Peintre en bâtiment</v>
       </c>
       <c r="K12" t="str">
-        <v>J'explore</v>
+        <v>Je sais</v>
       </c>
       <c r="L12" t="str">
         <v>référés Delphine</v>
       </c>
       <c r="M12" t="str">
-        <v>2603/mars 2026 STO</v>
+        <v>2604/avril 2026 STO</v>
       </c>
       <c r="O12" t="str">
         <v>HUDELLE Delphine</v>
       </c>
       <c r="P12">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q12">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R12" s="1">
-        <v>38302</v>
+        <v>39338</v>
       </c>
       <c r="S12" t="str">
-        <v>NOEL</v>
+        <v>PECQUEUR--BOULY</v>
       </c>
       <c r="T12" t="str">
         <v>BLENDECQUES</v>
@@ -2313,7 +2325,7 @@
         <v>OUI</v>
       </c>
       <c r="W12" t="str">
-        <v>39 Rue de l’Arbalète</v>
+        <v>127 Quai du Haut Pont</v>
       </c>
       <c r="X12" t="str">
         <v>62500</v>
@@ -2322,22 +2334,19 @@
         <v>Saint-Omer</v>
       </c>
       <c r="Z12" t="str">
+        <v>Non</v>
+      </c>
+      <c r="AB12" t="str">
         <v>Oui</v>
       </c>
-      <c r="AA12" t="str">
-        <v>QN06237M</v>
-      </c>
-      <c r="AB12" t="str">
-        <v>Non</v>
-      </c>
       <c r="AC12" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD12" t="str">
-        <v>[OLD]Niveau Infra 3</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE12" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AF12" t="str">
         <v>Non</v>
@@ -2355,49 +2364,55 @@
         <v>Non</v>
       </c>
       <c r="AK12" t="str">
-        <v>218h30m</v>
+        <v>223h15m</v>
       </c>
       <c r="AL12" t="str">
-        <v>151h</v>
+        <v>216h</v>
       </c>
       <c r="AM12" t="str">
-        <v>14h45m</v>
+        <v>29h15m</v>
       </c>
       <c r="AN12" s="1">
-        <v>46090.45143518518</v>
+        <v>46125.40244212963</v>
       </c>
       <c r="AO12" s="1">
-        <v>46136.47361111111</v>
+        <v>46171.669444444444</v>
       </c>
       <c r="AP12" s="1">
-        <v>46365.427083333336</v>
+        <v>46400.674305555556</v>
       </c>
       <c r="AU12" s="1">
-        <v>46056.39097222222</v>
+        <v>46098.447916666664</v>
       </c>
       <c r="AV12" t="str">
-        <v>ALTERN'EMPLOI SAINT-OMER</v>
+        <v>MIPE</v>
       </c>
       <c r="AW12" t="str">
-        <v>ANNE VERBECK</v>
+        <v xml:space="preserve">MARYLISE PARENT </v>
       </c>
       <c r="AX12" s="1">
-        <v>46051.39375</v>
+        <v>46083.450694444444</v>
       </c>
       <c r="AY12" t="str">
-        <v>anne.verbeck@alternemploi.com</v>
+        <v>parent.m@lamipe-pso.fr</v>
+      </c>
+      <c r="AZ12" t="str">
+        <v>06 78 00 38 88</v>
       </c>
       <c r="BA12" t="str">
         <v>NON</v>
       </c>
       <c r="BG12" t="str">
-        <v>11028</v>
+        <v>14589</v>
+      </c>
+      <c r="BH12" s="1">
+        <v>45834.083333333336</v>
       </c>
       <c r="BI12" t="str">
-        <v>1729669A</v>
+        <v>1732912A</v>
       </c>
       <c r="BJ12" t="str">
-        <v>fd7fd917-0788-4822-aae4-ae1932b90ac8</v>
+        <v>c8aa611f-fe4e-4c5c-9184-ee4695053378</v>
       </c>
       <c r="BK12" t="str">
         <v>Accepted</v>
@@ -2406,30 +2421,30 @@
         <v/>
       </c>
       <c r="BM12" t="str">
-        <v>romain.nl2004@gmail.com</v>
+        <v>typhainepecqueur13@gmail.com</v>
       </c>
       <c r="BN12" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/r_noel_e2c-grandlille_fr/IgA5WIXjW9NoSo5nyNnFxK9LAa5drKv20dNxkbZn4IAXUb8?e=vGW3BP</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/t_pecqueurbouly_e2c-grandlille_fr/IgCe4oeU-aNlR4WsO3nl3H9DAdHBT6mla7jdCEtpJ_1Y-mI?e=Quz9l8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>77529</v>
+        <v>118484</v>
       </c>
       <c r="B13" t="str">
         <v>Homme</v>
       </c>
       <c r="C13" t="str">
-        <v>LOYER</v>
+        <v>DEMARETZ</v>
       </c>
       <c r="D13" t="str">
-        <v>Sacha</v>
+        <v>CLEMENT</v>
       </c>
       <c r="E13" t="str">
-        <v>s.loyer@e2c-grandlille.fr</v>
+        <v>c.demaretz@e2c-grandlille.fr</v>
       </c>
       <c r="F13" t="str">
-        <v>0650761236</v>
+        <v>0745057553</v>
       </c>
       <c r="G13" t="str">
         <v>Grand Lille</v>
@@ -2438,7 +2453,7 @@
         <v>Saint Omer</v>
       </c>
       <c r="I13" t="str">
-        <v>Employé / Employée de libre-service, Employé / Employée de rayon libre-service, Agent / Agente d'entretien des espaces verts</v>
+        <v>Employé polyvalent / Employée polyvalente de libre-service, Opérateur / Opératrice d'exécution de façonnage</v>
       </c>
       <c r="K13" t="str">
         <v>J'ai des idées</v>
@@ -2447,25 +2462,25 @@
         <v>référés Cécile</v>
       </c>
       <c r="M13" t="str">
-        <v>2602/février 2026 STO</v>
+        <v>2604/avril 2026 STO</v>
       </c>
       <c r="O13" t="str">
         <v>LECERF Cécile</v>
       </c>
       <c r="P13">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q13">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="R13" s="1">
-        <v>38960</v>
+        <v>37467</v>
       </c>
       <c r="S13" t="str">
-        <v>LOYER</v>
+        <v>DEMARETZ</v>
       </c>
       <c r="T13" t="str">
-        <v>BLENDECQUES</v>
+        <v>ROUBAIX</v>
       </c>
       <c r="U13" t="str">
         <v>FRANCAISE</v>
@@ -2473,6 +2488,9 @@
       <c r="V13" t="str">
         <v>OUI</v>
       </c>
+      <c r="W13" t="str">
+        <v>124 Rue de l’Europe</v>
+      </c>
       <c r="X13" t="str">
         <v>62510</v>
       </c>
@@ -2489,7 +2507,7 @@
         <v>NON</v>
       </c>
       <c r="AD13" t="str">
-        <v>3 non validé</v>
+        <v>4 non validé</v>
       </c>
       <c r="AE13" t="str">
         <v>Oui</v>
@@ -2498,7 +2516,7 @@
         <v>Non</v>
       </c>
       <c r="AG13" t="str">
-        <v>SANS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH13" t="str">
         <v>Non</v>
@@ -2510,52 +2528,49 @@
         <v>Non</v>
       </c>
       <c r="AK13" t="str">
-        <v>301h</v>
+        <v>121h30m</v>
       </c>
       <c r="AL13" t="str">
-        <v>154h</v>
+        <v>245h</v>
       </c>
       <c r="AM13" t="str">
-        <v>36h</v>
+        <v>70h15m</v>
       </c>
       <c r="AN13" s="1">
-        <v>46055.63622685185</v>
+        <v>46125.40194444444</v>
       </c>
       <c r="AO13" s="1">
-        <v>46101.489583333336</v>
+        <v>46206.393055555556</v>
       </c>
       <c r="AP13" s="1">
-        <v>46328.39513888889</v>
+        <v>46400.68125</v>
       </c>
       <c r="AU13" s="1">
-        <v>46013.645833333336</v>
+        <v>46098.425</v>
       </c>
       <c r="AV13" t="str">
-        <v>MIPE</v>
+        <v>RESEAUX SOCIAUX</v>
       </c>
       <c r="AW13" t="str">
-        <v>LEROY GREGORY</v>
+        <v>FACEBOOK</v>
       </c>
       <c r="AX13" s="1">
-        <v>46009.40972222222</v>
-      </c>
-      <c r="AY13" t="str">
-        <v>leroy.g@lamipe-pso.fr</v>
+        <v>46092.427777777775</v>
       </c>
       <c r="BA13" t="str">
-        <v>OUI</v>
+        <v>NON</v>
       </c>
       <c r="BG13" t="str">
-        <v>9976</v>
+        <v>14594</v>
       </c>
       <c r="BH13" s="1">
-        <v>45936.083333333336</v>
+        <v>45737.041666666664</v>
       </c>
       <c r="BI13" t="str">
-        <v>1749326S</v>
+        <v>1612230Z</v>
       </c>
       <c r="BJ13" t="str">
-        <v>0d51d97c-da36-48bb-ba40-9a5595090088</v>
+        <v>71a2269b-9a22-4374-b734-1a503fcccd8d</v>
       </c>
       <c r="BK13" t="str">
         <v>Accepted</v>
@@ -2564,30 +2579,30 @@
         <v/>
       </c>
       <c r="BM13" t="str">
-        <v/>
+        <v>clementdemaretz@gmail.com</v>
       </c>
       <c r="BN13" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/personal/s_loyer_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fs%5Floyer%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2Factivit%C3%A9s%20stagiaire%20sacha%20loyer&amp;ga=1</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_demaretz_e2c-grandlille_fr/IgCD2k10xLkDTb_Txm_m5N4KAXWC2hKjRwDSyUQkYw9Gdf8?e=KnSU5i</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>57844</v>
+        <v>81726</v>
       </c>
       <c r="B14" t="str">
         <v>Homme</v>
       </c>
       <c r="C14" t="str">
-        <v>VANDAMME</v>
+        <v>LEROY</v>
       </c>
       <c r="D14" t="str">
-        <v>Matheo</v>
+        <v>Bryan</v>
       </c>
       <c r="E14" t="str">
-        <v>m.vandamme@e2c-grandlille.fr</v>
+        <v>b.leroy@e2c-grandlille.fr</v>
       </c>
       <c r="F14" t="str">
-        <v>0744829184</v>
+        <v>0669220460</v>
       </c>
       <c r="G14" t="str">
         <v>Grand Lille</v>
@@ -2596,34 +2611,34 @@
         <v>Saint Omer</v>
       </c>
       <c r="I14" t="str">
-        <v>Aide à domicile, Boulanger-pâtissier / Boulangère-pâtissière</v>
+        <v>Enduiseur / Enduiseuse</v>
       </c>
       <c r="K14" t="str">
-        <v>J'ai des idées</v>
+        <v>J'y vais</v>
       </c>
       <c r="L14" t="str">
-        <v>référés Delphine</v>
+        <v>référés Xavier</v>
       </c>
       <c r="M14" t="str">
         <v>2603/mars 2026 STO</v>
       </c>
       <c r="O14" t="str">
-        <v>HUDELLE Delphine</v>
+        <v>ROZIAU Bénédicte</v>
       </c>
       <c r="P14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R14" s="1">
-        <v>39450</v>
+        <v>38618</v>
       </c>
       <c r="S14" t="str">
-        <v>VANDAMME</v>
+        <v>LEROY</v>
       </c>
       <c r="T14" t="str">
-        <v>BLENDECQUES, FRANCE</v>
+        <v>Lille</v>
       </c>
       <c r="U14" t="str">
         <v>FRANCAISE</v>
@@ -2632,13 +2647,13 @@
         <v>OUI</v>
       </c>
       <c r="W14" t="str">
-        <v>3 3 Impasse Jules Guesdes</v>
+        <v>428 Rue du Parfum des Sapins</v>
       </c>
       <c r="X14" t="str">
-        <v>62575</v>
+        <v>62570</v>
       </c>
       <c r="Y14" t="str">
-        <v>BLENDECQUES</v>
+        <v>Helfaut</v>
       </c>
       <c r="Z14" t="str">
         <v>Non</v>
@@ -2650,10 +2665,10 @@
         <v>NON</v>
       </c>
       <c r="AD14" t="str">
-        <v>3 non validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE14" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AF14" t="str">
         <v>Non</v>
@@ -2671,55 +2686,55 @@
         <v>Non</v>
       </c>
       <c r="AK14" t="str">
-        <v>178h</v>
+        <v>180h15m</v>
       </c>
       <c r="AL14" t="str">
-        <v>89h</v>
+        <v>209h</v>
       </c>
       <c r="AM14" t="str">
-        <v>9h45m</v>
+        <v>91h</v>
       </c>
       <c r="AN14" s="1">
-        <v>46090.45521990741</v>
+        <v>46090.445925925924</v>
       </c>
       <c r="AO14" s="1">
-        <v>46139.469675925924</v>
+        <v>46171.657638888886</v>
       </c>
       <c r="AP14" s="1">
-        <v>46335.634722222225</v>
+        <v>46365.447222222225</v>
       </c>
       <c r="AU14" s="1">
-        <v>45954</v>
+        <v>46070.68958333333</v>
       </c>
       <c r="AV14" t="str">
-        <v>MISSION LOCALE DE ST OMER</v>
+        <v>MIPE</v>
       </c>
       <c r="AW14" t="str">
-        <v>MARYLISE PARENT</v>
+        <v>GREGORY LEROY</v>
       </c>
       <c r="AX14" s="1">
-        <v>45953</v>
+        <v>46063.69236111111</v>
       </c>
       <c r="AY14" t="str">
-        <v>parent.m@lamipe-pso.fr</v>
+        <v>leroy.g@lamipe-pso.fr</v>
       </c>
       <c r="AZ14" t="str">
-        <v>06 78 00 38 88</v>
+        <v>06 74 93 14 56</v>
       </c>
       <c r="BA14" t="str">
         <v>NON</v>
       </c>
       <c r="BG14" t="str">
-        <v>11453</v>
+        <v>11914</v>
       </c>
       <c r="BH14" s="1">
-        <v>45896.083333333336</v>
+        <v>45944.083333333336</v>
       </c>
       <c r="BI14" t="str">
-        <v>1740440H</v>
+        <v>5952912G</v>
       </c>
       <c r="BJ14" t="str">
-        <v>e6f5941d-009b-4d3a-9831-ccc0b8d9400f</v>
+        <v>2f0f42dd-4cab-44e6-8162-ed08596a4a34</v>
       </c>
       <c r="BK14" t="str">
         <v>Accepted</v>
@@ -2728,30 +2743,30 @@
         <v/>
       </c>
       <c r="BM14" t="str">
-        <v>matheo872@gmail.com</v>
+        <v>bryanleroy818@gmail.com</v>
       </c>
       <c r="BN14" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_vandamme_e2c-grandlille_fr/IgAEQ-0s7-vgTavcm831V4IsAdAA0_5uPkZtMf_f3Pmo2HA?e=krlTFt</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/b_leroy_e2c-grandlille_fr/IgCZeMh98XI1To8-bMZAbt5bAQOhibxgjufYIEG7lhPUOwI?e=LOUtFq</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>55180</v>
+        <v>80337</v>
       </c>
       <c r="B15" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C15" t="str">
-        <v>SGARD</v>
+        <v>NOEL</v>
       </c>
       <c r="D15" t="str">
-        <v>Alicia</v>
+        <v>Romain</v>
       </c>
       <c r="E15" t="str">
-        <v>aliciademaret11@gmail.com</v>
+        <v>r.noel@e2c-grandlille.fr</v>
       </c>
       <c r="F15" t="str">
-        <v>0780724630</v>
+        <v>0615066410</v>
       </c>
       <c r="G15" t="str">
         <v>Grand Lille</v>
@@ -2760,49 +2775,49 @@
         <v>Saint Omer</v>
       </c>
       <c r="I15" t="str">
-        <v>Auxiliaire de puériculture, Esthéticien / Esthéticienne</v>
+        <v>Menuisier / Menuisière, Soudeur / Soudeuse</v>
       </c>
       <c r="K15" t="str">
-        <v>J'ai des idées</v>
+        <v>J'explore</v>
       </c>
       <c r="L15" t="str">
-        <v>référés Bénédicte</v>
+        <v>référés Delphine</v>
       </c>
       <c r="M15" t="str">
-        <v>2512/décembre 2025 STO</v>
+        <v>2603/mars 2026 STO</v>
       </c>
       <c r="O15" t="str">
-        <v>ROZIAU Bénédicte</v>
+        <v>HUDELLE Delphine</v>
       </c>
       <c r="P15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R15" s="1">
-        <v>39825</v>
+        <v>38302</v>
       </c>
       <c r="S15" t="str">
-        <v>Sgard</v>
+        <v>NOEL</v>
       </c>
       <c r="T15" t="str">
-        <v>CALAIS</v>
+        <v>BLENDECQUES</v>
       </c>
       <c r="U15" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="V15" t="str">
-        <v>EN_COURS_ACTUALISATION</v>
+        <v>OUI</v>
       </c>
       <c r="W15" t="str">
-        <v>20 bis 20 bis Rue de l'Arbalète</v>
+        <v>39 Rue de l’Arbalète</v>
       </c>
       <c r="X15" t="str">
         <v>62500</v>
       </c>
       <c r="Y15" t="str">
-        <v>SAINT OMER</v>
+        <v>Saint-Omer</v>
       </c>
       <c r="Z15" t="str">
         <v>Oui</v>
@@ -2820,13 +2835,13 @@
         <v>3 non validé</v>
       </c>
       <c r="AE15" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AF15" t="str">
         <v>Non</v>
       </c>
       <c r="AG15" t="str">
-        <v>SANS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH15" t="str">
         <v>Non</v>
@@ -2838,64 +2853,52 @@
         <v>Non</v>
       </c>
       <c r="AK15" t="str">
-        <v>368h15m</v>
+        <v>300h30m</v>
       </c>
       <c r="AL15" t="str">
-        <v>196h30m</v>
+        <v>275h30m</v>
       </c>
       <c r="AM15" t="str">
-        <v>64h45m</v>
+        <v>29h30m</v>
       </c>
       <c r="AN15" s="1">
-        <v>46006</v>
+        <v>46090.45143518518</v>
       </c>
       <c r="AO15" s="1">
-        <v>46069.67797453704</v>
+        <v>46136.47361111111</v>
       </c>
       <c r="AP15" s="1">
-        <v>46280.083333333336</v>
+        <v>46365.427083333336</v>
+      </c>
+      <c r="AU15" s="1">
+        <v>46056.39097222222</v>
       </c>
       <c r="AV15" t="str">
-        <v>MIPE</v>
+        <v xml:space="preserve">Altern'Emploi </v>
       </c>
       <c r="AW15" t="str">
-        <v xml:space="preserve">STEPHANIE BERTIN </v>
+        <v>ANNE VERBECK</v>
+      </c>
+      <c r="AX15" s="1">
+        <v>46051.39375</v>
       </c>
       <c r="AY15" t="str">
-        <v>bertin.s@lamipe-pso.fr</v>
-      </c>
-      <c r="AZ15" t="str">
-        <v xml:space="preserve">06 74 93 14 32 </v>
+        <v>anne.verbeck@alternemploi.com</v>
       </c>
       <c r="BA15" t="str">
         <v>NON</v>
       </c>
-      <c r="BB15" t="str">
-        <v>DEMARET</v>
-      </c>
-      <c r="BC15" t="str">
-        <v>Aurélie</v>
-      </c>
-      <c r="BD15" t="str">
-        <v>20 bis Rue de l'Arbalète</v>
-      </c>
-      <c r="BE15" t="str">
-        <v>0768469252</v>
-      </c>
-      <c r="BF15" t="str">
-        <v>ademaret83@gmail.com</v>
-      </c>
       <c r="BG15" t="str">
-        <v>598075</v>
+        <v>11028</v>
       </c>
       <c r="BH15" s="1">
-        <v>45971.041666666664</v>
+        <v>45793.083333333336</v>
       </c>
       <c r="BI15" t="str">
-        <v>1754236D</v>
+        <v>1729669A</v>
       </c>
       <c r="BJ15" t="str">
-        <v>053d293e-0bfc-4488-af7e-6d4b2cfa8b20</v>
+        <v>fd7fd917-0788-4822-aae4-ae1932b90ac8</v>
       </c>
       <c r="BK15" t="str">
         <v>Accepted</v>
@@ -2904,30 +2907,30 @@
         <v/>
       </c>
       <c r="BM15" t="str">
-        <v/>
+        <v>romain.nl2004@gmail.com</v>
       </c>
       <c r="BN15" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/r_noel_e2c-grandlille_fr/IgA5WIXjW9NoSo5nyNnFxK9LAa5drKv20dNxkbZn4IAXUb8?e=vGW3BP</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>40008</v>
+        <v>77529</v>
       </c>
       <c r="B16" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C16" t="str">
-        <v>CARPENTIER</v>
+        <v>LOYER</v>
       </c>
       <c r="D16" t="str">
-        <v>Léa</v>
+        <v>Sacha</v>
       </c>
       <c r="E16" t="str">
-        <v>carpentierlea7@gmail.com</v>
+        <v>s.loyer@e2c-grandlille.fr</v>
       </c>
       <c r="F16" t="str">
-        <v>0661223358</v>
+        <v>0650761236</v>
       </c>
       <c r="G16" t="str">
         <v>Grand Lille</v>
@@ -2936,31 +2939,31 @@
         <v>Saint Omer</v>
       </c>
       <c r="I16" t="str">
-        <v>Agent / Agente d'entretien-propreté de locaux</v>
+        <v>Employé / Employée de libre-service, Employé / Employée de rayon libre-service, Agent / Agente d'entretien des espaces verts</v>
       </c>
       <c r="K16" t="str">
-        <v>Je sais</v>
+        <v>J'explore</v>
       </c>
       <c r="L16" t="str">
-        <v>référés Bénédicte</v>
+        <v>référés Cécile</v>
       </c>
       <c r="M16" t="str">
-        <v>2512/décembre 2025 STO</v>
+        <v>2602/février 2026 STO</v>
       </c>
       <c r="O16" t="str">
-        <v>ROZIAU Bénédicte</v>
+        <v>LECERF Cécile</v>
       </c>
       <c r="P16">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q16">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R16" s="1">
-        <v>37949</v>
+        <v>38960</v>
       </c>
       <c r="S16" t="str">
-        <v>CARPENTIER</v>
+        <v>LOYER</v>
       </c>
       <c r="T16" t="str">
         <v>BLENDECQUES</v>
@@ -2971,29 +2974,26 @@
       <c r="V16" t="str">
         <v>OUI</v>
       </c>
-      <c r="W16" t="str">
-        <v>38 38 Rue Antoine Van Dyck</v>
-      </c>
       <c r="X16" t="str">
-        <v>62219</v>
+        <v>62510</v>
       </c>
       <c r="Y16" t="str">
-        <v>LONGUENESSE</v>
+        <v>Arques</v>
       </c>
       <c r="Z16" t="str">
         <v>Non</v>
       </c>
       <c r="AB16" t="str">
+        <v>Non</v>
+      </c>
+      <c r="AC16" t="str">
+        <v>NON</v>
+      </c>
+      <c r="AD16" t="str">
+        <v>3 non validé</v>
+      </c>
+      <c r="AE16" t="str">
         <v>Oui</v>
-      </c>
-      <c r="AC16" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
-      </c>
-      <c r="AD16" t="str">
-        <v>4 non validé</v>
-      </c>
-      <c r="AE16" t="str">
-        <v>Non</v>
       </c>
       <c r="AF16" t="str">
         <v>Non</v>
@@ -3002,7 +3002,7 @@
         <v>SANS</v>
       </c>
       <c r="AH16" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="AI16" t="str">
         <v>Non</v>
@@ -3011,49 +3011,52 @@
         <v>Non</v>
       </c>
       <c r="AK16" t="str">
-        <v>351h</v>
+        <v>411h45m</v>
       </c>
       <c r="AL16" t="str">
-        <v>235h20m</v>
+        <v>251h30m</v>
       </c>
       <c r="AM16" t="str">
-        <v>53h</v>
+        <v>61h45m</v>
       </c>
       <c r="AN16" s="1">
-        <v>46006</v>
+        <v>46055.63622685185</v>
       </c>
       <c r="AO16" s="1">
-        <v>46066.677777777775</v>
+        <v>46101.489583333336</v>
       </c>
       <c r="AP16" s="1">
-        <v>46280.083333333336</v>
+        <v>46328.39513888889</v>
+      </c>
+      <c r="AU16" s="1">
+        <v>46013.645833333336</v>
       </c>
       <c r="AV16" t="str">
         <v>MIPE</v>
       </c>
       <c r="AW16" t="str">
-        <v>Sabrina Malfoy</v>
+        <v>LEROY GREGORY</v>
+      </c>
+      <c r="AX16" s="1">
+        <v>46009.40972222222</v>
       </c>
       <c r="AY16" t="str">
-        <v>malfoy.s@lamipe-pso.fr</v>
-      </c>
-      <c r="AZ16" t="str">
-        <v>0784588649</v>
+        <v>leroy.g@lamipe-pso.fr</v>
       </c>
       <c r="BA16" t="str">
-        <v>NON</v>
+        <v>OUI</v>
       </c>
       <c r="BG16" t="str">
-        <v>598181</v>
+        <v>9976</v>
       </c>
       <c r="BH16" s="1">
-        <v>45658.041666666664</v>
+        <v>45936.083333333336</v>
       </c>
       <c r="BI16" t="str">
-        <v>1710996D</v>
+        <v>1749326S</v>
       </c>
       <c r="BJ16" t="str">
-        <v>209089b5-0253-453e-81a5-cee1fb3fb11c</v>
+        <v>0d51d97c-da36-48bb-ba40-9a5595090088</v>
       </c>
       <c r="BK16" t="str">
         <v>Accepted</v>
@@ -3065,27 +3068,27 @@
         <v/>
       </c>
       <c r="BN16" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/personal/s_loyer_e2c-grandlille_fr/_layouts/15/onedrive.aspx?id=%2Fpersonal%2Fs%5Floyer%5Fe2c%2Dgrandlille%5Ffr%2FDocuments%2Factivit%C3%A9s%20stagiaire%20sacha%20loyer&amp;ga=1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>36683</v>
+        <v>40008</v>
       </c>
       <c r="B17" t="str">
         <v>Femme</v>
       </c>
       <c r="C17" t="str">
-        <v>DEVULDER</v>
+        <v>CARPENTIER</v>
       </c>
       <c r="D17" t="str">
-        <v>Lioneline</v>
+        <v>Léa</v>
       </c>
       <c r="E17" t="str">
-        <v>devulderlioneline@gmail.com</v>
+        <v>carpentierlea7@gmail.com</v>
       </c>
       <c r="F17" t="str">
-        <v>0670698593</v>
+        <v>0661223358</v>
       </c>
       <c r="G17" t="str">
         <v>Grand Lille</v>
@@ -3094,34 +3097,34 @@
         <v>Saint Omer</v>
       </c>
       <c r="I17" t="str">
-        <v>Fleuriste</v>
+        <v>Agent / Agente d'entretien-propreté de locaux</v>
       </c>
       <c r="K17" t="str">
         <v>Je sais</v>
       </c>
       <c r="L17" t="str">
-        <v>référés Cécile</v>
+        <v>référés Bénédicte</v>
       </c>
       <c r="M17" t="str">
-        <v>2511/novembre 2025 STO</v>
+        <v>2512/décembre 2025 STO</v>
       </c>
       <c r="O17" t="str">
-        <v>LECERF Cécile</v>
+        <v>ROZIAU Bénédicte</v>
       </c>
       <c r="P17">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q17">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R17" s="1">
-        <v>39397</v>
+        <v>37949</v>
       </c>
       <c r="S17" t="str">
-        <v>DEVULDER</v>
+        <v>CARPENTIER</v>
       </c>
       <c r="T17" t="str">
-        <v>CALAIS</v>
+        <v>BLENDECQUES</v>
       </c>
       <c r="U17" t="str">
         <v>FRANCAISE</v>
@@ -3130,25 +3133,25 @@
         <v>OUI</v>
       </c>
       <c r="W17" t="str">
-        <v>39 39 Rue Anatole France Résidence les Roseaux Logement 18</v>
+        <v>38 38 Rue Antoine Van Dyck</v>
       </c>
       <c r="X17" t="str">
-        <v>62510</v>
+        <v>62219</v>
       </c>
       <c r="Y17" t="str">
-        <v>ARQUES</v>
+        <v>LONGUENESSE</v>
       </c>
       <c r="Z17" t="str">
         <v>Non</v>
       </c>
       <c r="AB17" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AC17" t="str">
-        <v>NON</v>
+        <v>CEJ_MISSION_LOCALE</v>
       </c>
       <c r="AD17" t="str">
-        <v>[OLD]Niveau 4 validé</v>
+        <v>4 non validé</v>
       </c>
       <c r="AE17" t="str">
         <v>Non</v>
@@ -3160,7 +3163,7 @@
         <v>SANS</v>
       </c>
       <c r="AH17" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AI17" t="str">
         <v>Non</v>
@@ -3169,40 +3172,49 @@
         <v>Non</v>
       </c>
       <c r="AK17" t="str">
-        <v>425h</v>
+        <v>406h</v>
       </c>
       <c r="AL17" t="str">
-        <v>378h</v>
+        <v>395h10m</v>
       </c>
       <c r="AM17" t="str">
-        <v>41h45m</v>
+        <v>49h45m</v>
       </c>
       <c r="AN17" s="1">
-        <v>45964</v>
+        <v>46006</v>
       </c>
       <c r="AO17" s="1">
-        <v>46066.39513888889</v>
+        <v>46066.677777777775</v>
       </c>
       <c r="AP17" s="1">
-        <v>46237.083333333336</v>
+        <v>46280.083333333336</v>
       </c>
       <c r="AV17" t="str">
-        <v>RESEAUX SOCIAUX</v>
+        <v>MIPE</v>
+      </c>
+      <c r="AW17" t="str">
+        <v>Sabrina Malfoy</v>
+      </c>
+      <c r="AY17" t="str">
+        <v>malfoy.s@lamipe-pso.fr</v>
+      </c>
+      <c r="AZ17" t="str">
+        <v>0784588649</v>
       </c>
       <c r="BA17" t="str">
         <v>NON</v>
       </c>
       <c r="BG17" t="str">
-        <v>596917</v>
+        <v>598181</v>
       </c>
       <c r="BH17" s="1">
-        <v>45846.083333333336</v>
+        <v>45658.041666666664</v>
       </c>
       <c r="BI17" t="str">
-        <v>1734272D</v>
+        <v>1710996D</v>
       </c>
       <c r="BJ17" t="str">
-        <v>7957b293-fe4d-4666-a31b-2d3f3dcf9b6c</v>
+        <v>209089b5-0253-453e-81a5-cee1fb3fb11c</v>
       </c>
       <c r="BK17" t="str">
         <v>Accepted</v>
@@ -3243,7 +3255,7 @@
         <v>Saint Omer</v>
       </c>
       <c r="I18" t="str">
-        <v>Conducteur routier / Conductrice routière</v>
+        <v>Aide d'élevage bovin, Aide d'élevage en production laitière</v>
       </c>
       <c r="K18" t="str">
         <v>J'explore</v>
@@ -3297,7 +3309,7 @@
         <v>NON</v>
       </c>
       <c r="AD18" t="str">
-        <v>[OLD]Niveau 4 validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE18" t="str">
         <v>Non</v>
@@ -3318,13 +3330,13 @@
         <v>Non</v>
       </c>
       <c r="AK18" t="str">
-        <v>486h</v>
+        <v>578h15m</v>
       </c>
       <c r="AL18" t="str">
-        <v>217h</v>
+        <v>346h</v>
       </c>
       <c r="AM18" t="str">
-        <v>53h45m</v>
+        <v>72h</v>
       </c>
       <c r="AN18" s="1">
         <v>45964</v>
@@ -3337,6 +3349,9 @@
       </c>
       <c r="AV18" t="str">
         <v>En direct</v>
+      </c>
+      <c r="AW18" t="str">
+        <v>SPONTANEE</v>
       </c>
       <c r="BA18" t="str">
         <v>NON</v>
@@ -3395,10 +3410,10 @@
         <v>Employé / Employée de libre-service</v>
       </c>
       <c r="K19" t="str">
-        <v>Je sais</v>
+        <v>J'y vais</v>
       </c>
       <c r="L19" t="str">
-        <v>référés Cécile</v>
+        <v>référés Xavier</v>
       </c>
       <c r="M19" t="str">
         <v>2511/novembre 2025 STO</v>
@@ -3407,7 +3422,7 @@
         <v>LECERF Cécile</v>
       </c>
       <c r="P19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q19">
         <v>22</v>
@@ -3467,13 +3482,13 @@
         <v>Non</v>
       </c>
       <c r="AK19" t="str">
-        <v>430h45m</v>
+        <v>474h30m</v>
       </c>
       <c r="AL19" t="str">
         <v>325h</v>
       </c>
       <c r="AM19" t="str">
-        <v>89h15m</v>
+        <v>115h</v>
       </c>
       <c r="AN19" s="1">
         <v>45964</v>
@@ -3559,7 +3574,7 @@
         <v>LECERF Cécile</v>
       </c>
       <c r="P20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q20">
         <v>22</v>
@@ -3598,7 +3613,7 @@
         <v>NON</v>
       </c>
       <c r="AD20" t="str">
-        <v>[OLD]Niveau 3 validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE20" t="str">
         <v>Non</v>
@@ -3619,13 +3634,13 @@
         <v>Non</v>
       </c>
       <c r="AK20" t="str">
-        <v>496h</v>
+        <v>550h</v>
       </c>
       <c r="AL20" t="str">
-        <v>505h</v>
+        <v>553h</v>
       </c>
       <c r="AM20" t="str">
-        <v>86h45m</v>
+        <v>83h30m</v>
       </c>
       <c r="AN20" s="1">
         <v>45931</v>
@@ -3667,462 +3682,12 @@
         <v/>
       </c>
       <c r="BN20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>35222</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C21" t="str">
-        <v>CHARLET</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Sarah</v>
-      </c>
-      <c r="E21" t="str">
-        <v>sarah.charlet62@gmail.com</v>
-      </c>
-      <c r="F21" t="str">
-        <v>0767403411</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Saint Omer</v>
-      </c>
-      <c r="I21" t="str">
-        <v>Palefrenier / Palefrenière, Agent / Agente d'entretien des espaces verts</v>
-      </c>
-      <c r="K21" t="str">
-        <v>J'ai des idées</v>
-      </c>
-      <c r="L21" t="str">
-        <v>référés Bénédicte</v>
-      </c>
-      <c r="M21" t="str">
-        <v>2510/octobre 2025 STO</v>
-      </c>
-      <c r="O21" t="str">
-        <v>ROZIAU Bénédicte</v>
-      </c>
-      <c r="P21">
-        <v>19</v>
-      </c>
-      <c r="Q21">
-        <v>18</v>
-      </c>
-      <c r="R21" s="1">
-        <v>39046</v>
-      </c>
-      <c r="S21" t="str">
-        <v>CHARLET</v>
-      </c>
-      <c r="T21" t="str">
-        <v>BLENDECQUES</v>
-      </c>
-      <c r="U21" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V21" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="W21" t="str">
-        <v>3 3 Rue Louis le Sénéchal</v>
-      </c>
-      <c r="X21" t="str">
-        <v>62380</v>
-      </c>
-      <c r="Y21" t="str">
-        <v>LUMBRES</v>
-      </c>
-      <c r="Z21" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB21" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AC21" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD21" t="str">
-        <v>[OLD]Niveau 3 validé</v>
-      </c>
-      <c r="AE21" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF21" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG21" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH21" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AI21" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ21" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK21" t="str">
-        <v>558h15m</v>
-      </c>
-      <c r="AL21" t="str">
-        <v>449h</v>
-      </c>
-      <c r="AM21" t="str">
-        <v>32h30m</v>
-      </c>
-      <c r="AN21" s="1">
-        <v>45931</v>
-      </c>
-      <c r="AO21" s="1">
-        <v>46069.60091435185</v>
-      </c>
-      <c r="AP21" s="1">
-        <v>46204.083333333336</v>
-      </c>
-      <c r="AV21" t="str">
-        <v>MISSION LOCALE DE ST OMER</v>
-      </c>
-      <c r="AW21" t="str">
-        <v>HELENE</v>
-      </c>
-      <c r="BA21" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG21" t="str">
-        <v>595588</v>
-      </c>
-      <c r="BH21" s="1">
-        <v>45658.041666666664</v>
-      </c>
-      <c r="BI21" t="str">
-        <v>1712474K</v>
-      </c>
-      <c r="BJ21" t="str">
-        <v>0321ecc5-ce63-499d-8608-41c5fae992ee</v>
-      </c>
-      <c r="BK21" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL21" t="str">
-        <v/>
-      </c>
-      <c r="BM21" t="str">
-        <v/>
-      </c>
-      <c r="BN21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>33707</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C22" t="str">
-        <v>GAY</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Lilou</v>
-      </c>
-      <c r="E22" t="str">
-        <v>lg01042008@gmail.com</v>
-      </c>
-      <c r="F22" t="str">
-        <v>0768278437</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Saint Omer</v>
-      </c>
-      <c r="I22" t="str">
-        <v>Aide médico-psychologique, Moniteur éducateur / Monitrice éducatrice, Agent administratif / Agente administrative</v>
-      </c>
-      <c r="K22" t="str">
-        <v>J'ai des idées</v>
-      </c>
-      <c r="L22" t="str">
-        <v>référés Cécile</v>
-      </c>
-      <c r="M22" t="str">
-        <v>2509/septembre 2025 STO</v>
-      </c>
-      <c r="O22" t="str">
-        <v>LECERF Cécile</v>
-      </c>
-      <c r="P22">
-        <v>18</v>
-      </c>
-      <c r="Q22">
-        <v>17</v>
-      </c>
-      <c r="R22" s="1">
-        <v>39539</v>
-      </c>
-      <c r="S22" t="str">
-        <v>Gay</v>
-      </c>
-      <c r="T22" t="str">
-        <v>BLENDECQUES</v>
-      </c>
-      <c r="U22" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V22" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="W22" t="str">
-        <v>34 34 Rue de Therouanne</v>
-      </c>
-      <c r="X22" t="str">
-        <v>62500</v>
-      </c>
-      <c r="Y22" t="str">
-        <v>SAINT-OMER</v>
-      </c>
-      <c r="Z22" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB22" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AC22" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD22" t="str">
-        <v>[OLD]Niveau Infra 3</v>
-      </c>
-      <c r="AE22" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF22" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG22" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH22" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI22" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ22" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK22" t="str">
-        <v>553h</v>
-      </c>
-      <c r="AL22" t="str">
-        <v>397h5m</v>
-      </c>
-      <c r="AM22" t="str">
-        <v>101h45m</v>
-      </c>
-      <c r="AN22" s="1">
-        <v>45908</v>
-      </c>
-      <c r="AO22" s="1">
-        <v>45958.041666666664</v>
-      </c>
-      <c r="AP22" s="1">
-        <v>46181.083333333336</v>
-      </c>
-      <c r="AV22" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="BA22" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG22" t="str">
-        <v>594481</v>
-      </c>
-      <c r="BH22" s="1">
-        <v>45903.083333333336</v>
-      </c>
-      <c r="BI22" t="str">
-        <v>1742591W</v>
-      </c>
-      <c r="BJ22" t="str">
-        <v>8d50f8a9-0093-415a-b9de-44cea0795979</v>
-      </c>
-      <c r="BK22" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL22" t="str">
-        <v/>
-      </c>
-      <c r="BM22" t="str">
-        <v/>
-      </c>
-      <c r="BN22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>33654</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C23" t="str">
-        <v>LENGAGNE</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Dorine</v>
-      </c>
-      <c r="E23" t="str">
-        <v>dorinelengagne91@gmail.com</v>
-      </c>
-      <c r="F23" t="str">
-        <v>0644072552</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Saint Omer</v>
-      </c>
-      <c r="I23" t="str">
-        <v>Infirmier / Infirmière en soins généraux (IDE)</v>
-      </c>
-      <c r="K23" t="str">
-        <v>J'y vais</v>
-      </c>
-      <c r="L23" t="str">
-        <v>référés Xavier</v>
-      </c>
-      <c r="M23" t="str">
-        <v>2509/septembre 2025 STO</v>
-      </c>
-      <c r="O23" t="str">
-        <v>CAROULLE Xavier</v>
-      </c>
-      <c r="P23">
-        <v>19</v>
-      </c>
-      <c r="Q23">
-        <v>19</v>
-      </c>
-      <c r="R23" s="1">
-        <v>38931</v>
-      </c>
-      <c r="S23" t="str">
-        <v>LENGAGNE</v>
-      </c>
-      <c r="T23" t="str">
-        <v>BLENDECQUES</v>
-      </c>
-      <c r="U23" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V23" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="W23" t="str">
-        <v>6 6 Rue de Fauquembergues</v>
-      </c>
-      <c r="X23" t="str">
-        <v>62380</v>
-      </c>
-      <c r="Y23" t="str">
-        <v>WAVRANS SUR L'AA</v>
-      </c>
-      <c r="Z23" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB23" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC23" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD23" t="str">
-        <v>[OLD]Niveau 4 validé</v>
-      </c>
-      <c r="AE23" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF23" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG23" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH23" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI23" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ23" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK23" t="str">
-        <v>454h30m</v>
-      </c>
-      <c r="AL23" t="str">
-        <v>431h</v>
-      </c>
-      <c r="AM23" t="str">
-        <v>71h</v>
-      </c>
-      <c r="AN23" s="1">
-        <v>45908</v>
-      </c>
-      <c r="AO23" s="1">
-        <v>45958.041666666664</v>
-      </c>
-      <c r="AP23" s="1">
-        <v>46181.083333333336</v>
-      </c>
-      <c r="AV23" t="str">
-        <v>MISSION LOCALE DE ST OMER</v>
-      </c>
-      <c r="BA23" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG23" t="str">
-        <v>594476</v>
-      </c>
-      <c r="BH23" s="1">
-        <v>45891.083333333336</v>
-      </c>
-      <c r="BI23" t="str">
-        <v>1739868L</v>
-      </c>
-      <c r="BJ23" t="str">
-        <v>f3939e9e-79f9-4c80-aa83-29c2781a2815</v>
-      </c>
-      <c r="BK23" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL23" t="str">
-        <v/>
-      </c>
-      <c r="BM23" t="str">
-        <v/>
-      </c>
-      <c r="BN23" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BN23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BN20"/>
   </ignoredErrors>
 </worksheet>
 </file>